--- a/Tables/EPS_anova_hostbiomass_FromR.xlsx
+++ b/Tables/EPS_anova_hostbiomass_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -392,12 +392,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.410</t>
+          <t>0.402</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35.095</t>
+          <t>36.050</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>0.498</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.026</t>
+          <t>22.344</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -434,43 +434,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Morphology:Variety</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>28.936</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.850</t>
+          <t>&lt; 0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>PC2</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.210</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Morphology:Variety</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.166</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Residuals</t>
         </is>
       </c>
-      <c r="B5">
-        <v>345</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.035</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B7">
+        <v>343</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.820</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
